--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486993_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486993_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.4151</v>
+        <v>12.9464</v>
       </c>
       <c r="E2" t="n">
-        <v>11.8681</v>
+        <v>12.6662</v>
       </c>
       <c r="F2" t="n">
-        <v>0.547</v>
+        <v>0.2802</v>
       </c>
       <c r="G2" t="n">
         <v>3.6529</v>
@@ -610,13 +610,13 @@
         <v>2.8748</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8907</v>
+        <v>-0.3593</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2943</v>
+        <v>-0.4962</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4036</v>
+        <v>0.1368</v>
       </c>
       <c r="V2" t="n">
         <v>8.010199999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5884</v>
+        <v>1.7425</v>
       </c>
       <c r="E3" t="n">
-        <v>2.752</v>
+        <v>1.8765</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1636</v>
+        <v>-0.134</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2634</v>
@@ -688,13 +688,13 @@
         <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0038</v>
+        <v>0.1579</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3906</v>
+        <v>0.5151</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3869</v>
+        <v>-0.3572</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4182</v>
+        <v>-0.2621</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5585</v>
+        <v>0.9968</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1403</v>
+        <v>-1.2589</v>
       </c>
       <c r="G4" t="n">
         <v>-1.4794</v>
@@ -766,13 +766,13 @@
         <v>0.616</v>
       </c>
       <c r="S4" t="n">
-        <v>1.029</v>
+        <v>0.3487</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8173</v>
+        <v>0.2556</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2117</v>
+        <v>0.0931</v>
       </c>
       <c r="V4" t="n">
         <v>0.4579</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. PEREZ RAMIREZ</t>
+          <t>A. BELLVER VALIENTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4079</v>
+        <v>-0.3594</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.0911</v>
+        <v>-0.1741</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6832</v>
+        <v>-0.1853</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.4323</v>
+        <v>0.1782</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4664</v>
+        <v>-0.1981</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9659</v>
+        <v>0.3763</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5837</v>
+        <v>0.7093</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3378</v>
+        <v>0.0779</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.9215</v>
+        <v>0.6315</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8486</v>
+        <v>-0.5311</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8041</v>
+        <v>-0.2759</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0445</v>
+        <v>-0.2552</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4107</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6427</v>
+        <v>0.616</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2174</v>
+        <v>-0.1269</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2753</v>
+        <v>0.1433</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4927</v>
+        <v>-0.2702</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3963</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.3963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BELLVER VALIENTE</t>
+          <t>G. PEREZ RAMIREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6575</v>
+        <v>-0.6088</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3833</v>
+        <v>-2.0252</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2742</v>
+        <v>1.4164</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1782</v>
+        <v>-2.4323</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1981</v>
+        <v>-1.4664</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3763</v>
+        <v>-0.9659</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7093</v>
+        <v>-0.5837</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0779</v>
+        <v>0.3378</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6315</v>
+        <v>-0.9215</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5311</v>
+        <v>-1.8486</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2759</v>
+        <v>-1.8041</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2552</v>
+        <v>-0.0445</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4107</v>
+        <v>0.4107</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="R6" t="n">
-        <v>0.616</v>
+        <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.425</v>
+        <v>0.0165</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0659</v>
+        <v>-0.2094</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3591</v>
+        <v>0.2259</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.3963</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.3963</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1424</v>
+        <v>-1.1128</v>
       </c>
       <c r="E7" t="n">
         <v>-0.923</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2194</v>
+        <v>-0.1898</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9568</v>
@@ -1000,13 +1000,13 @@
         <v>0.2053</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3909</v>
+        <v>-0.3613</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1317</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2592</v>
+        <v>-0.2295</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2666</v>
+        <v>-1.4636</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3962</v>
+        <v>-1.9192</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1296</v>
+        <v>0.4557</v>
       </c>
       <c r="G8" t="n">
         <v>-3.0251</v>
@@ -1078,13 +1078,13 @@
         <v>2.0534</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4032</v>
+        <v>0.2063</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7437</v>
+        <v>0.2207</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3405</v>
+        <v>-0.0144</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6982</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5149</v>
+        <v>-1.5568</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1003</v>
+        <v>0.4141</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6152</v>
+        <v>-1.9709</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0557</v>
@@ -1156,13 +1156,13 @@
         <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0349</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7246</v>
+        <v>-0.4108</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8014</v>
+        <v>0.4457</v>
       </c>
       <c r="V9" t="n">
         <v>-1.7679</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4261</v>
+        <v>-1.8594</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2772</v>
+        <v>-2.8588</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8511</v>
+        <v>0.9993</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2006</v>
@@ -1234,13 +1234,13 @@
         <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6567</v>
+        <v>-0.0901</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5774</v>
+        <v>-0.159</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0793</v>
+        <v>0.0689</v>
       </c>
       <c r="V10" t="n">
         <v>1.0472</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5143</v>
+        <v>-2.5003</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2955</v>
+        <v>-2.4001</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2188</v>
+        <v>-0.1003</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3458</v>
@@ -1312,13 +1312,13 @@
         <v>1.8481</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1767</v>
+        <v>-0.1627</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1122</v>
+        <v>0.0076</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2889</v>
+        <v>-0.1704</v>
       </c>
       <c r="V11" t="n">
         <v>0.2402</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.472899999999999</v>
+        <v>-7.6172</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7695</v>
+        <v>-3.1806</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.7034</v>
+        <v>-4.4366</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0187</v>
@@ -1390,13 +1390,13 @@
         <v>1.8481</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5076</v>
+        <v>-0.6519</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8486</v>
+        <v>-0.2597</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.659</v>
+        <v>-0.3922</v>
       </c>
       <c r="V12" t="n">
         <v>-3.5359</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.980899999999998</v>
+        <v>-2.651499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1431</v>
+        <v>2.472599999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.124000000000001</v>
+        <v>-5.1242</v>
       </c>
       <c r="G13" t="n">
         <v>-11.9467</v>
@@ -1447,7 +1447,7 @@
         <v>8.714499999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.1073</v>
+        <v>-2.107300000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-18.5542</v>
@@ -1456,10 +1456,10 @@
         <v>-9.281500000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.272699999999999</v>
+        <v>-9.2727</v>
       </c>
       <c r="P13" t="n">
-        <v>5.1335</v>
+        <v>5.133500000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-11.2938</v>
@@ -1468,13 +1468,13 @@
         <v>16.4273</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3174</v>
+        <v>-0.9879</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.854</v>
+        <v>-0.5245</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4634999999999999</v>
+        <v>-0.4635</v>
       </c>
       <c r="V13" t="n">
         <v>5.149799999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7666</v>
+        <v>6.0299</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4579</v>
+        <v>4.3533</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3087</v>
+        <v>1.6766</v>
       </c>
       <c r="G14" t="n">
         <v>4.5837</v>
@@ -1546,13 +1546,13 @@
         <v>1.0267</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3964</v>
+        <v>0.6596</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0195</v>
+        <v>-0.1241</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4159</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2402</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4842</v>
+        <v>4.5766</v>
       </c>
       <c r="E15" t="n">
         <v>3.3349</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1494</v>
+        <v>1.2417</v>
       </c>
       <c r="G15" t="n">
         <v>3.6864</v>
@@ -1624,13 +1624,13 @@
         <v>1.0267</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5576</v>
+        <v>0.65</v>
       </c>
       <c r="T15" t="n">
         <v>0.1781</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3795</v>
+        <v>0.4719</v>
       </c>
       <c r="V15" t="n">
         <v>0.2402</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2959</v>
+        <v>4.2199</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4334</v>
+        <v>4.6426</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1375</v>
+        <v>-0.4227</v>
       </c>
       <c r="G16" t="n">
         <v>4.1258</v>
@@ -1702,13 +1702,13 @@
         <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3371</v>
+        <v>0.587</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1858</v>
+        <v>0.395</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5229</v>
+        <v>0.1919</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6982</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1383</v>
+        <v>0.9117</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3038</v>
+        <v>1.0946</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1654</v>
+        <v>-0.1829</v>
       </c>
       <c r="G17" t="n">
         <v>1.1266</v>
@@ -1780,13 +1780,13 @@
         <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5928</v>
+        <v>0.3662</v>
       </c>
       <c r="T17" t="n">
-        <v>0.12</v>
+        <v>-0.0892</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4729</v>
+        <v>0.4554</v>
       </c>
       <c r="V17" t="n">
         <v>0.2402</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ JIMENEZ</t>
+          <t>G. GANTT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4366</v>
+        <v>0.4594</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0464</v>
+        <v>-0.1987</v>
       </c>
       <c r="F18" t="n">
-        <v>0.483</v>
+        <v>0.6581</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3461</v>
+        <v>-0.1847</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0486</v>
+        <v>-0.5583</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3947</v>
+        <v>0.3736</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0195</v>
+        <v>0.3748</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0195</v>
+        <v>0.4672</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3656</v>
+        <v>-0.5596</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0291</v>
+        <v>-1.0255</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3947</v>
+        <v>0.4659</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.2321</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>0.08450000000000001</v>
+        <v>-0.588</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0659</v>
+        <v>-0.5735</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1504</v>
+        <v>-0.0144</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. RUIZ GONZALEZ</t>
+          <t>J. RODRIGUEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0417</v>
+        <v>0.3773</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1125</v>
+        <v>-0.0464</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0709</v>
+        <v>0.4237</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.3461</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3504</v>
+        <v>0.0486</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2789</v>
+        <v>-0.3947</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0389</v>
+        <v>0.0195</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0389</v>
+        <v>0.0195</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1104</v>
+        <v>-0.3656</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3893</v>
+        <v>0.0291</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2789</v>
+        <v>-0.3947</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1936,28 +1936,28 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1131</v>
+        <v>0.0252</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0736</v>
+        <v>-0.0659</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0395</v>
+        <v>0.0911</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. GANTT</t>
+          <t>I. RUIZ GONZALEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0759</v>
+        <v>0.3102</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4079</v>
+        <v>0.3217</v>
       </c>
       <c r="F20" t="n">
-        <v>0.332</v>
+        <v>-0.0116</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1847</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5583</v>
+        <v>-0.3504</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3736</v>
+        <v>0.2789</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3748</v>
+        <v>0.0389</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4672</v>
+        <v>0.0389</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.09229999999999999</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5596</v>
+        <v>-0.1104</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0255</v>
+        <v>-0.3893</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4659</v>
+        <v>0.2789</v>
       </c>
       <c r="P20" t="n">
-        <v>1.2321</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2321</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1232</v>
+        <v>0.3816</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7827</v>
+        <v>0.2828</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3405</v>
+        <v>0.0988</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3585</v>
+        <v>-0.4083</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0829</v>
+        <v>0.4401</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2756</v>
+        <v>-0.8485</v>
       </c>
       <c r="G21" t="n">
         <v>0.4496</v>
@@ -2092,13 +2092,13 @@
         <v>0.8214</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6644</v>
+        <v>0.2858</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2558</v>
+        <v>0.2673</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4087</v>
+        <v>0.0185</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9384</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. ZIZIC</t>
+          <t>L. TVRDIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8044</v>
+        <v>-1.8664</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0565</v>
+        <v>-0.4269</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7479</v>
+        <v>-1.4396</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2011</v>
+        <v>-1.1013</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2141</v>
+        <v>-1.1354</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.013</v>
+        <v>0.0341</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9583</v>
+        <v>-0.4314</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8794</v>
+        <v>0.2794</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0789</v>
+        <v>-0.7108</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7572</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6653</v>
+        <v>-1.4148</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.092</v>
+        <v>0.7449</v>
       </c>
       <c r="P22" t="n">
+        <v>0.2053</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-1.0267</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-2.0534</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1999</v>
+        <v>0.2082</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0386</v>
+        <v>-0.1474</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1613</v>
+        <v>0.3556</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1786</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1786</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. STOILOV</t>
+          <t>N. ZIZIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5894</v>
+        <v>-2.2367</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4116</v>
+        <v>-1.3703</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1778</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0541</v>
+        <v>0.2011</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2464</v>
+        <v>0.2141</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1923</v>
+        <v>-0.013</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9867</v>
+        <v>0.9583</v>
       </c>
       <c r="K23" t="n">
-        <v>0.75</v>
+        <v>0.8794</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2368</v>
+        <v>0.0789</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0408</v>
+        <v>-0.7572</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9964</v>
+        <v>-0.6653</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0445</v>
+        <v>-0.092</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.9015</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.1336</v>
+        <v>-2.0534</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2321</v>
+        <v>1.0267</v>
       </c>
       <c r="S23" t="n">
-        <v>2.0643</v>
+        <v>-0.2325</v>
       </c>
       <c r="T23" t="n">
-        <v>1.844</v>
+        <v>-0.2752</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2203</v>
+        <v>0.0427</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6982</v>
+        <v>-1.1786</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5893</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. TVRDIC</t>
+          <t>E. STOILOV</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9003</v>
+        <v>-3.503</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0545</v>
+        <v>-3.2485</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8458</v>
+        <v>-0.2546</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.1013</v>
+        <v>-0.0541</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1354</v>
+        <v>-0.2464</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0341</v>
+        <v>0.1923</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4314</v>
+        <v>0.9867</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2794</v>
+        <v>0.75</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7108</v>
+        <v>0.2368</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-1.0408</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4148</v>
+        <v>-0.9964</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7449</v>
+        <v>-0.0445</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2053</v>
+        <v>-3.9015</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0267</v>
+        <v>-5.1336</v>
       </c>
       <c r="R24" t="n">
         <v>1.2321</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8257</v>
+        <v>1.1507</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.775</v>
+        <v>1.0072</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0507</v>
+        <v>0.1435</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.1786</v>
+        <v>-0.6982</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1786</v>
+        <v>-0.1088</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.3573</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.454</v>
+        <v>-3.7975</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.4586</v>
+        <v>-3.7724</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0046</v>
+        <v>-0.025</v>
       </c>
       <c r="G25" t="n">
         <v>-0.4688</v>
@@ -2404,13 +2404,13 @@
         <v>1.2321</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2592</v>
+        <v>-0.0843</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.3915</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3368</v>
+        <v>0.3072</v>
       </c>
       <c r="V25" t="n">
         <v>-1.3963</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>2.980800000000004</v>
+        <v>5.0731</v>
       </c>
       <c r="E26" t="n">
-        <v>5.124100000000002</v>
+        <v>5.124</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.1432</v>
+        <v>-0.05119999999999928</v>
       </c>
       <c r="G26" t="n">
         <v>11.9468</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5670000000000006</v>
+        <v>0.5670000000000004</v>
       </c>
       <c r="I26" t="n">
         <v>11.3798</v>
@@ -2458,7 +2458,7 @@
         <v>18.5541</v>
       </c>
       <c r="K26" t="n">
-        <v>9.281500000000001</v>
+        <v>9.281499999999999</v>
       </c>
       <c r="L26" t="n">
         <v>9.2727</v>
@@ -2473,7 +2473,7 @@
         <v>2.1072</v>
       </c>
       <c r="P26" t="n">
-        <v>-5.1336</v>
+        <v>-5.133599999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>-16.4273</v>
@@ -2482,19 +2482,19 @@
         <v>11.2941</v>
       </c>
       <c r="S26" t="n">
-        <v>1.3174</v>
+        <v>3.409500000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4635</v>
+        <v>0.4636000000000002</v>
       </c>
       <c r="U26" t="n">
-        <v>0.8537999999999999</v>
+        <v>2.946</v>
       </c>
       <c r="V26" t="n">
         <v>-5.149900000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>2.533700000000001</v>
+        <v>2.5337</v>
       </c>
       <c r="X26" t="n">
         <v>-7.6836</v>
